--- a/src/assets/worklog/13.Formation.xlsx
+++ b/src/assets/worklog/13.Formation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\data\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F91CC4-882B-4B33-AFD1-80E561A8E778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A474E069-F7A0-4902-B445-3C3E6C913130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17085" yWindow="75" windowWidth="19140" windowHeight="15210" xr2:uid="{937EC8C4-16D6-4AFA-9FBD-1FBA4800754F}"/>
+    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{937EC8C4-16D6-4AFA-9FBD-1FBA4800754F}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -111,7 +111,7 @@
     <definedName name="preFormationTemperature">원본!$K$52</definedName>
     <definedName name="preFormationUpperVoltage">원본!$G$52</definedName>
     <definedName name="preFormationVoltageCondition">원본!$C$52</definedName>
-    <definedName name="productionId">원본!$G$7</definedName>
+    <definedName name="projectId">원본!$G$7</definedName>
     <definedName name="remark">원본!$A$67</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
     <definedName name="safety">원본!$K$64</definedName>
@@ -822,15 +822,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -840,27 +831,42 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -873,139 +879,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1017,41 +921,137 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1398,17 +1398,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1420,1227 +1420,1213 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="A2" s="80"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="9"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5" t="s">
+      <c r="F7" s="29"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5" t="s">
+      <c r="F9" s="29"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="4" t="s">
+      <c r="J9" s="29"/>
+      <c r="K9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="4"/>
+      <c r="L9" s="79"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="9"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="75"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="16"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="9"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="29"/>
+      <c r="C15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="21" t="s">
+      <c r="D15" s="20"/>
+      <c r="E15" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="17" t="s">
+      <c r="F15" s="39"/>
+      <c r="G15" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="21" t="s">
+      <c r="H15" s="20"/>
+      <c r="I15" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="22"/>
-      <c r="K15" s="25" t="s">
+      <c r="J15" s="39"/>
+      <c r="K15" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="25"/>
+      <c r="L15" s="37"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="45"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="69"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="52" t="s">
+      <c r="A21" s="64"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="53"/>
-      <c r="E21" s="35" t="s">
+      <c r="D21" s="72"/>
+      <c r="E21" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="35" t="s">
+      <c r="F21" s="72"/>
+      <c r="G21" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="H21" s="53"/>
-      <c r="I21" s="35" t="s">
+      <c r="H21" s="72"/>
+      <c r="I21" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="53"/>
-      <c r="K21" s="35" t="s">
+      <c r="J21" s="72"/>
+      <c r="K21" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="36"/>
+      <c r="L21" s="59"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="45"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="38"/>
+      <c r="A22" s="64"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="60"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="45"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="44"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="63"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="45"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="38"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="60"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="45"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="30"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="49"/>
     </row>
     <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="23"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="31"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="45"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
+      <c r="A38" s="64"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="69"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="45"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="52" t="s">
+      <c r="A39" s="64"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="53"/>
-      <c r="E39" s="35" t="s">
+      <c r="D39" s="72"/>
+      <c r="E39" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="F39" s="53"/>
-      <c r="G39" s="35" t="s">
+      <c r="F39" s="72"/>
+      <c r="G39" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="H39" s="53"/>
-      <c r="I39" s="35" t="s">
+      <c r="H39" s="72"/>
+      <c r="I39" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="J39" s="53"/>
-      <c r="K39" s="35" t="s">
+      <c r="J39" s="72"/>
+      <c r="K39" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="L39" s="36"/>
+      <c r="L39" s="59"/>
       <c r="M39" s="3"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="45"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="37"/>
-      <c r="L40" s="38"/>
+      <c r="A40" s="64"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="60"/>
       <c r="M40" s="3"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="45"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="44"/>
+      <c r="A41" s="64"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="63"/>
       <c r="M41" s="3"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="45"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="37"/>
-      <c r="L42" s="38"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="60"/>
       <c r="M42" s="3"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="45"/>
-      <c r="B43" s="47"/>
-      <c r="C43" s="54"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="30"/>
+      <c r="A43" s="64"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="49"/>
       <c r="M43" s="3"/>
     </row>
     <row r="44" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="23"/>
-      <c r="B44" s="48"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="31"/>
+      <c r="A44" s="40"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="48"/>
+      <c r="L44" s="50"/>
       <c r="M44" s="3"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="56"/>
-      <c r="L45" s="56"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="58"/>
-      <c r="K47" s="58"/>
-      <c r="L47" s="27"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="44"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="60"/>
-      <c r="E48" s="60"/>
-      <c r="F48" s="60"/>
-      <c r="G48" s="60"/>
-      <c r="H48" s="60"/>
-      <c r="I48" s="60"/>
-      <c r="J48" s="60"/>
-      <c r="K48" s="60"/>
-      <c r="L48" s="61"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="56"/>
+      <c r="K48" s="56"/>
+      <c r="L48" s="57"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="9"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="6"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="17" t="s">
+      <c r="B50" s="20"/>
+      <c r="C50" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="18"/>
-      <c r="E50" s="21" t="s">
+      <c r="D50" s="20"/>
+      <c r="E50" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="22"/>
-      <c r="G50" s="17" t="s">
+      <c r="F50" s="39"/>
+      <c r="G50" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="18"/>
-      <c r="I50" s="21" t="s">
+      <c r="H50" s="20"/>
+      <c r="I50" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="J50" s="22"/>
-      <c r="K50" s="17" t="s">
+      <c r="J50" s="39"/>
+      <c r="K50" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="L50" s="18"/>
+      <c r="L50" s="20"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="20"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="22"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="62"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="62"/>
-      <c r="H52" s="63"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="62"/>
-      <c r="L52" s="63"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="23"/>
+      <c r="L52" s="24"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="65"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="65"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="42"/>
-      <c r="K53" s="64"/>
-      <c r="L53" s="65"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="26"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="66" t="s">
+      <c r="A54" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B54" s="66"/>
-      <c r="C54" s="67"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="68" t="s">
+      <c r="B54" s="34"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="F54" s="66"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="25" t="s">
+      <c r="F54" s="34"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J54" s="25"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
+      <c r="J54" s="37"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="66"/>
-      <c r="B55" s="66"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="66"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="37"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="62"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="62"/>
-      <c r="H56" s="63"/>
-      <c r="I56" s="43"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="62"/>
-      <c r="L56" s="63"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="31"/>
+      <c r="K56" s="23"/>
+      <c r="L56" s="24"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="65"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="65"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="42"/>
-      <c r="K57" s="64"/>
-      <c r="L57" s="65"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="26"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="18"/>
-      <c r="C58" s="62"/>
-      <c r="D58" s="63"/>
-      <c r="E58" s="17" t="s">
+      <c r="B58" s="20"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="18"/>
-      <c r="G58" s="62"/>
-      <c r="H58" s="69"/>
-      <c r="I58" s="69"/>
-      <c r="J58" s="69"/>
-      <c r="K58" s="69"/>
-      <c r="L58" s="63"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+      <c r="K58" s="27"/>
+      <c r="L58" s="24"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="64"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="70"/>
-      <c r="I59" s="70"/>
-      <c r="J59" s="70"/>
-      <c r="K59" s="70"/>
-      <c r="L59" s="65"/>
+      <c r="A59" s="21"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="9"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="6"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B61" s="10"/>
-      <c r="C61" s="71" t="s">
+      <c r="B61" s="18"/>
+      <c r="C61" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D61" s="33"/>
-      <c r="E61" s="10" t="s">
+      <c r="D61" s="17"/>
+      <c r="E61" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F61" s="10"/>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="10" t="s">
+      <c r="F61" s="18"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="J61" s="10"/>
-      <c r="K61" s="71" t="s">
+      <c r="J61" s="18"/>
+      <c r="K61" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L61" s="33"/>
+      <c r="L61" s="17"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="33"/>
-      <c r="L62" s="33"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="9"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B64" s="10"/>
-      <c r="C64" s="33" t="s">
+      <c r="B64" s="18"/>
+      <c r="C64" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D64" s="33"/>
-      <c r="E64" s="10" t="s">
+      <c r="D64" s="17"/>
+      <c r="E64" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F64" s="10"/>
-      <c r="G64" s="33" t="s">
+      <c r="F64" s="18"/>
+      <c r="G64" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H64" s="33"/>
-      <c r="I64" s="10" t="s">
+      <c r="H64" s="17"/>
+      <c r="I64" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J64" s="10"/>
-      <c r="K64" s="33" t="s">
+      <c r="J64" s="18"/>
+      <c r="K64" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="L64" s="33"/>
+      <c r="L64" s="17"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="33"/>
-      <c r="H65" s="33"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="33"/>
-      <c r="L65" s="33"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="9"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="6"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="72" t="s">
+      <c r="A67" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B67" s="73"/>
-      <c r="C67" s="73"/>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="73"/>
-      <c r="H67" s="73"/>
-      <c r="I67" s="73"/>
-      <c r="J67" s="73"/>
-      <c r="K67" s="73"/>
-      <c r="L67" s="74"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="9"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="75"/>
-      <c r="B68" s="76"/>
-      <c r="C68" s="76"/>
-      <c r="D68" s="76"/>
-      <c r="E68" s="76"/>
-      <c r="F68" s="76"/>
-      <c r="G68" s="76"/>
-      <c r="H68" s="76"/>
-      <c r="I68" s="76"/>
-      <c r="J68" s="76"/>
-      <c r="K68" s="76"/>
-      <c r="L68" s="77"/>
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="12"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="75"/>
-      <c r="B69" s="76"/>
-      <c r="C69" s="76"/>
-      <c r="D69" s="76"/>
-      <c r="E69" s="76"/>
-      <c r="F69" s="76"/>
-      <c r="G69" s="76"/>
-      <c r="H69" s="76"/>
-      <c r="I69" s="76"/>
-      <c r="J69" s="76"/>
-      <c r="K69" s="76"/>
-      <c r="L69" s="77"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="12"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="75"/>
-      <c r="B70" s="76"/>
-      <c r="C70" s="76"/>
-      <c r="D70" s="76"/>
-      <c r="E70" s="76"/>
-      <c r="F70" s="76"/>
-      <c r="G70" s="76"/>
-      <c r="H70" s="76"/>
-      <c r="I70" s="76"/>
-      <c r="J70" s="76"/>
-      <c r="K70" s="76"/>
-      <c r="L70" s="77"/>
+      <c r="A70" s="10"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="12"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="75"/>
-      <c r="B71" s="76"/>
-      <c r="C71" s="76"/>
-      <c r="D71" s="76"/>
-      <c r="E71" s="76"/>
-      <c r="F71" s="76"/>
-      <c r="G71" s="76"/>
-      <c r="H71" s="76"/>
-      <c r="I71" s="76"/>
-      <c r="J71" s="76"/>
-      <c r="K71" s="76"/>
-      <c r="L71" s="77"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="12"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="75"/>
-      <c r="B72" s="76"/>
-      <c r="C72" s="76"/>
-      <c r="D72" s="76"/>
-      <c r="E72" s="76"/>
-      <c r="F72" s="76"/>
-      <c r="G72" s="76"/>
-      <c r="H72" s="76"/>
-      <c r="I72" s="76"/>
-      <c r="J72" s="76"/>
-      <c r="K72" s="76"/>
-      <c r="L72" s="77"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="12"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="78"/>
-      <c r="B73" s="79"/>
-      <c r="C73" s="79"/>
-      <c r="D73" s="79"/>
-      <c r="E73" s="79"/>
-      <c r="F73" s="79"/>
-      <c r="G73" s="79"/>
-      <c r="H73" s="79"/>
-      <c r="I73" s="79"/>
-      <c r="J73" s="79"/>
-      <c r="K73" s="79"/>
-      <c r="L73" s="80"/>
+      <c r="A73" s="13"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="158">
-    <mergeCell ref="A66:L66"/>
-    <mergeCell ref="A67:L73"/>
-    <mergeCell ref="K61:L62"/>
-    <mergeCell ref="A63:L63"/>
-    <mergeCell ref="A64:B65"/>
-    <mergeCell ref="C64:D65"/>
-    <mergeCell ref="E64:F65"/>
-    <mergeCell ref="G64:H65"/>
-    <mergeCell ref="I64:J65"/>
-    <mergeCell ref="K64:L65"/>
-    <mergeCell ref="A58:B59"/>
-    <mergeCell ref="C58:D59"/>
-    <mergeCell ref="E58:F59"/>
-    <mergeCell ref="G58:L59"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="A61:B62"/>
-    <mergeCell ref="C61:D62"/>
-    <mergeCell ref="E61:F62"/>
-    <mergeCell ref="G61:H62"/>
-    <mergeCell ref="I61:J62"/>
-    <mergeCell ref="A56:B57"/>
-    <mergeCell ref="C56:D57"/>
-    <mergeCell ref="E56:F57"/>
-    <mergeCell ref="G56:H57"/>
-    <mergeCell ref="I56:J57"/>
-    <mergeCell ref="K56:L57"/>
-    <mergeCell ref="A54:B55"/>
-    <mergeCell ref="C54:D55"/>
-    <mergeCell ref="E54:F55"/>
-    <mergeCell ref="G54:H55"/>
-    <mergeCell ref="I54:J55"/>
-    <mergeCell ref="K54:L55"/>
-    <mergeCell ref="A52:B53"/>
-    <mergeCell ref="C52:D53"/>
-    <mergeCell ref="E52:F53"/>
-    <mergeCell ref="G52:H53"/>
-    <mergeCell ref="I52:J53"/>
-    <mergeCell ref="K52:L53"/>
-    <mergeCell ref="A49:L49"/>
-    <mergeCell ref="A50:B51"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:F51"/>
-    <mergeCell ref="G50:H51"/>
-    <mergeCell ref="I50:J51"/>
-    <mergeCell ref="K50:L51"/>
-    <mergeCell ref="K45:L46"/>
-    <mergeCell ref="A47:B48"/>
-    <mergeCell ref="C43:D44"/>
-    <mergeCell ref="E43:F44"/>
-    <mergeCell ref="G43:H44"/>
-    <mergeCell ref="I43:J44"/>
-    <mergeCell ref="K43:L44"/>
-    <mergeCell ref="A45:B46"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:F46"/>
-    <mergeCell ref="G45:H46"/>
-    <mergeCell ref="I45:J46"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:F42"/>
-    <mergeCell ref="G41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="K41:L42"/>
-    <mergeCell ref="A37:B44"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="E37:F38"/>
-    <mergeCell ref="G37:H38"/>
-    <mergeCell ref="I37:J38"/>
-    <mergeCell ref="K37:L38"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:L13"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="I15:J16"/>
+    <mergeCell ref="K15:L16"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="K25:L26"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="K17:L18"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A19:B26"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="E19:F20"/>
+    <mergeCell ref="G19:H20"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
     <mergeCell ref="K31:L32"/>
     <mergeCell ref="K27:L28"/>
     <mergeCell ref="A29:B30"/>
@@ -2665,66 +2651,80 @@
     <mergeCell ref="C27:D28"/>
     <mergeCell ref="E27:F28"/>
     <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A19:B26"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="E19:F20"/>
-    <mergeCell ref="G19:H20"/>
-    <mergeCell ref="I19:J20"/>
-    <mergeCell ref="K19:L20"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="K25:L26"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="K17:L18"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:L13"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="I15:J16"/>
-    <mergeCell ref="K15:L16"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:F42"/>
+    <mergeCell ref="G41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="K41:L42"/>
+    <mergeCell ref="A37:B44"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="G37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="K37:L38"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K45:L46"/>
+    <mergeCell ref="A47:B48"/>
+    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="E43:F44"/>
+    <mergeCell ref="G43:H44"/>
+    <mergeCell ref="I43:J44"/>
+    <mergeCell ref="K43:L44"/>
+    <mergeCell ref="A45:B46"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:F46"/>
+    <mergeCell ref="G45:H46"/>
+    <mergeCell ref="I45:J46"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="A52:B53"/>
+    <mergeCell ref="C52:D53"/>
+    <mergeCell ref="E52:F53"/>
+    <mergeCell ref="G52:H53"/>
+    <mergeCell ref="I52:J53"/>
+    <mergeCell ref="K52:L53"/>
+    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A50:B51"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:F51"/>
+    <mergeCell ref="G50:H51"/>
+    <mergeCell ref="I50:J51"/>
+    <mergeCell ref="K50:L51"/>
+    <mergeCell ref="A56:B57"/>
+    <mergeCell ref="C56:D57"/>
+    <mergeCell ref="E56:F57"/>
+    <mergeCell ref="G56:H57"/>
+    <mergeCell ref="I56:J57"/>
+    <mergeCell ref="K56:L57"/>
+    <mergeCell ref="A54:B55"/>
+    <mergeCell ref="C54:D55"/>
+    <mergeCell ref="E54:F55"/>
+    <mergeCell ref="G54:H55"/>
+    <mergeCell ref="I54:J55"/>
+    <mergeCell ref="K54:L55"/>
+    <mergeCell ref="A58:B59"/>
+    <mergeCell ref="C58:D59"/>
+    <mergeCell ref="E58:F59"/>
+    <mergeCell ref="G58:L59"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="A61:B62"/>
+    <mergeCell ref="C61:D62"/>
+    <mergeCell ref="E61:F62"/>
+    <mergeCell ref="G61:H62"/>
+    <mergeCell ref="I61:J62"/>
+    <mergeCell ref="A66:L66"/>
+    <mergeCell ref="A67:L73"/>
+    <mergeCell ref="K61:L62"/>
+    <mergeCell ref="A63:L63"/>
+    <mergeCell ref="A64:B65"/>
+    <mergeCell ref="C64:D65"/>
+    <mergeCell ref="E64:F65"/>
+    <mergeCell ref="G64:H65"/>
+    <mergeCell ref="I64:J65"/>
+    <mergeCell ref="K64:L65"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
